--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Bank ETF.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Bank ETF.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="68">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Nifty Bank ETF</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -76,24 +76,24 @@
     <t>INE090A01021</t>
   </si>
   <si>
+    <t>Axis Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE238A01034</t>
+  </si>
+  <si>
+    <t>State Bank Of India</t>
+  </si>
+  <si>
+    <t>INE062A01020</t>
+  </si>
+  <si>
     <t>Kotak Mahindra Bank Ltd.</t>
   </si>
   <si>
     <t>INE237A01028</t>
   </si>
   <si>
-    <t>State Bank Of India</t>
-  </si>
-  <si>
-    <t>INE062A01020</t>
-  </si>
-  <si>
-    <t>Axis Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE238A01034</t>
-  </si>
-  <si>
     <t>IndusInd Bank Ltd.</t>
   </si>
   <si>
@@ -118,24 +118,24 @@
     <t>INE092T01019</t>
   </si>
   <si>
+    <t>AU Small Finance Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE949L01017</t>
+  </si>
+  <si>
+    <t>Canara Bank</t>
+  </si>
+  <si>
+    <t>INE476A01022</t>
+  </si>
+  <si>
     <t>Punjab National Bank</t>
   </si>
   <si>
     <t>INE160A01022</t>
   </si>
   <si>
-    <t>AU Small Finance Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE949L01017</t>
-  </si>
-  <si>
-    <t>Canara Bank</t>
-  </si>
-  <si>
-    <t>INE476A01022</t>
-  </si>
-  <si>
     <t>Unlisted</t>
   </si>
   <si>
@@ -190,10 +190,7 @@
     <t>Name of the Instrument</t>
   </si>
   <si>
-    <t>Au Small Finance Bank Ltd</t>
-  </si>
-  <si>
-    <t>Federal Bank  Ltd.</t>
+    <t>AU Small Finance Bank Ltd</t>
   </si>
   <si>
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
@@ -205,7 +202,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -446,7 +443,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -539,9 +536,6 @@
       <protection/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyBorder="1" applyProtection="1">
-      <protection/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -638,13 +632,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -662,7 +656,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="13563600"/>
+          <a:off x="666750" y="13373100"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -677,13 +671,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:row>82</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>93</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -701,7 +695,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="16421100"/>
+          <a:off x="666750" y="16230600"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1035,19 +1029,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J82"/>
+  <dimension ref="B1:J81"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="27" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="27" width="53.57142857142857" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="27" width="16.142857142857142" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="27" width="9.714285714285714" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="27" width="19.714285714285715" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="27" width="11.0" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="27" width="38.714285714285715" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="27" width="11.714285714285714" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="27" width="29.714285714285715" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="27" width="26.714285714285715" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" style="26" width="10.0" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="26" width="53.57142857142857" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="26" width="16.142857142857142" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="26" width="9.714285714285714" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="26" width="19.714285714285715" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="26" width="11.0" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="26" width="38.714285714285715" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="26" width="11.714285714285714" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="26" width="29.714285714285715" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="26" width="26.714285714285715" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1">
@@ -1135,10 +1129,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>252799.49000000002</v>
+        <v>315224.24</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9999612264685</v>
+        <v>0.9999616852176002</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1172,10 +1166,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>252799.49000000002</v>
+        <v>315224.24</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9999612264685</v>
+        <v>0.9999616852176002</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1198,13 +1192,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>4111073</v>
+        <v>4508794</v>
       </c>
       <c r="G8" s="15">
-        <v>69836.85</v>
+        <v>87691.53</v>
       </c>
       <c r="H8" s="16">
-        <v>0.2762432083179</v>
+        <v>0.2781771164494</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1227,13 +1221,13 @@
         <v>17</v>
       </c>
       <c r="F9" s="14">
-        <v>5054657</v>
+        <v>5488975</v>
       </c>
       <c r="G9" s="15">
-        <v>63324.74</v>
+        <v>79359.6</v>
       </c>
       <c r="H9" s="16">
-        <v>0.2504842263575</v>
+        <v>0.2517463738012</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1256,13 +1250,13 @@
         <v>17</v>
       </c>
       <c r="F10" s="14">
-        <v>1277823</v>
+        <v>2222172</v>
       </c>
       <c r="G10" s="15">
-        <v>24295.25</v>
+        <v>26492.73</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0961010957236</v>
+        <v>0.0840408559215</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1285,13 +1279,13 @@
         <v>17</v>
       </c>
       <c r="F11" s="14">
-        <v>2756810</v>
+        <v>3216162</v>
       </c>
       <c r="G11" s="15">
-        <v>21307.38</v>
+        <v>26124.88</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0842824241363</v>
+        <v>0.0828739535732</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1314,13 +1308,13 @@
         <v>17</v>
       </c>
       <c r="F12" s="14">
-        <v>2080217</v>
+        <v>1145443</v>
       </c>
       <c r="G12" s="15">
-        <v>20513.02</v>
+        <v>23764.51</v>
       </c>
       <c r="H12" s="16">
-        <v>0.081140292798</v>
+        <v>0.0753863328149</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1343,13 +1337,13 @@
         <v>17</v>
       </c>
       <c r="F13" s="14">
-        <v>1218719</v>
+        <v>1546197</v>
       </c>
       <c r="G13" s="15">
-        <v>12079.94</v>
+        <v>12631.66</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0477828164054</v>
+        <v>0.0400704464247</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1372,13 +1366,13 @@
         <v>17</v>
       </c>
       <c r="F14" s="14">
-        <v>4514830</v>
+        <v>5756253</v>
       </c>
       <c r="G14" s="15">
-        <v>8452.21</v>
+        <v>11631.08</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0334331460794</v>
+        <v>0.036896383215</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1401,13 +1395,13 @@
         <v>17</v>
       </c>
       <c r="F15" s="14">
-        <v>3436963</v>
+        <v>4348051</v>
       </c>
       <c r="G15" s="15">
-        <v>7334.14</v>
+        <v>10850.56</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0290105633895</v>
+        <v>0.0344203994691</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1430,13 +1424,13 @@
         <v>17</v>
       </c>
       <c r="F16" s="14">
-        <v>11419067</v>
+        <v>14555876</v>
       </c>
       <c r="G16" s="15">
-        <v>7221.42</v>
+        <v>9893.63</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0285646937026</v>
+        <v>0.0313848038073</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1459,13 +1453,13 @@
         <v>17</v>
       </c>
       <c r="F17" s="14">
-        <v>6352742</v>
+        <v>1317991</v>
       </c>
       <c r="G17" s="15">
-        <v>6428.97</v>
+        <v>9134.34</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0254301174663</v>
+        <v>0.0289761663625</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1488,13 +1482,13 @@
         <v>17</v>
       </c>
       <c r="F18" s="14">
-        <v>1033696</v>
+        <v>7915223</v>
       </c>
       <c r="G18" s="15">
-        <v>6212</v>
+        <v>9083.51</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0245718816079</v>
+        <v>0.0288149222512</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1517,13 +1511,13 @@
         <v>17</v>
       </c>
       <c r="F19" s="14">
-        <v>6211607</v>
+        <v>8095077</v>
       </c>
       <c r="G19" s="15">
-        <v>5793.57</v>
+        <v>8566.21</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0229167604841</v>
+        <v>0.0271739311276</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -2038,10 +2032,10 @@
         <v>13</v>
       </c>
       <c r="G47" s="9">
-        <v>122.59</v>
+        <v>513.39</v>
       </c>
       <c r="H47" s="10">
-        <v>0.0004849109733</v>
+        <v>0.0016285877303</v>
       </c>
       <c r="I47" s="9" t="s">
         <v>13</v>
@@ -2075,10 +2069,10 @@
         <v>13</v>
       </c>
       <c r="G49" s="18">
-        <v>-112.78769110000576</v>
+        <v>-501.3117893001181</v>
       </c>
       <c r="H49" s="19">
-        <v>-0.00044613744245679824</v>
+        <v>-0.0015902729487058899</v>
       </c>
       <c r="I49" s="18" t="s">
         <v>13</v>
@@ -2104,10 +2098,10 @@
         <v>13</v>
       </c>
       <c r="G50" s="18">
-        <v>252809.2923089</v>
+        <v>315236.3182107</v>
       </c>
       <c r="H50" s="19">
-        <v>0.9999999999993431</v>
+        <v>0.9999999999991944</v>
       </c>
       <c r="I50" s="18" t="s">
         <v>13</v>
@@ -2134,111 +2128,103 @@
       <c r="B54" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C54" s="26">
-        <v>452000</v>
-      </c>
-    </row>
-    <row r="55" spans="2:3" ht="15" customHeight="1">
-      <c r="B55" s="25" t="s">
+      <c r="C54" s="25">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" ht="15" customHeight="1">
+      <c r="B56" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C55" s="26">
-        <v>289382</v>
-      </c>
-    </row>
-    <row r="57" spans="2:9" ht="15" customHeight="1">
+      <c r="C56" s="26"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="26"/>
+      <c r="H56" s="26"/>
+      <c r="I56" s="26"/>
+    </row>
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C57" s="27"/>
-      <c r="D57" s="27"/>
-      <c r="E57" s="27"/>
-      <c r="F57" s="27"/>
-      <c r="G57" s="27"/>
-      <c r="H57" s="27"/>
-      <c r="I57" s="27"/>
-    </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1">
-      <c r="B58" s="13" t="s">
+      <c r="C57" s="26"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="26"/>
+      <c r="H57" s="26"/>
+    </row>
+    <row r="58" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B58" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="C58" s="27"/>
-      <c r="D58" s="27"/>
-      <c r="E58" s="27"/>
-      <c r="F58" s="27"/>
-      <c r="G58" s="27"/>
-      <c r="H58" s="27"/>
+      <c r="C58" s="26"/>
+      <c r="D58" s="26"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="26"/>
+      <c r="H58" s="26"/>
     </row>
     <row r="59" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B59" s="28" t="s">
+      <c r="B59" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="C59" s="27"/>
-      <c r="D59" s="27"/>
-      <c r="E59" s="27"/>
-      <c r="F59" s="27"/>
-      <c r="G59" s="27"/>
-      <c r="H59" s="27"/>
+      <c r="C59" s="26"/>
+      <c r="D59" s="26"/>
+      <c r="E59" s="26"/>
+      <c r="F59" s="26"/>
+      <c r="G59" s="26"/>
+      <c r="H59" s="26"/>
     </row>
     <row r="60" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B60" s="28" t="s">
+      <c r="B60" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="C60" s="27"/>
-      <c r="D60" s="27"/>
-      <c r="E60" s="27"/>
-      <c r="F60" s="27"/>
-      <c r="G60" s="27"/>
-      <c r="H60" s="27"/>
-    </row>
-    <row r="61" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B61" s="28" t="s">
+      <c r="C60" s="26"/>
+      <c r="D60" s="26"/>
+      <c r="E60" s="26"/>
+      <c r="F60" s="26"/>
+      <c r="G60" s="26"/>
+      <c r="H60" s="26"/>
+    </row>
+    <row r="62" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B62" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C61" s="27"/>
-      <c r="D61" s="27"/>
-      <c r="E61" s="27"/>
-      <c r="F61" s="27"/>
-      <c r="G61" s="27"/>
-      <c r="H61" s="27"/>
-    </row>
-    <row r="63" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B63" s="28" t="s">
+      <c r="C62" s="26"/>
+      <c r="D62" s="26"/>
+      <c r="E62" s="26"/>
+      <c r="F62" s="26"/>
+      <c r="G62" s="26"/>
+      <c r="H62" s="26"/>
+    </row>
+    <row r="65" ht="15">
+      <c r="B65" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="C63" s="27"/>
-      <c r="D63" s="27"/>
-      <c r="E63" s="27"/>
-      <c r="F63" s="27"/>
-      <c r="G63" s="27"/>
-      <c r="H63" s="27"/>
-    </row>
-    <row r="66" ht="15">
-      <c r="B66" s="27" t="s">
+    </row>
+    <row r="80" ht="15">
+      <c r="B80" s="26" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="81" ht="15">
-      <c r="B81" s="27" t="s">
+      <c r="B81" s="26" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="82" ht="15">
-      <c r="B82" s="27" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B58:H58"/>
     <mergeCell ref="B59:H59"/>
     <mergeCell ref="B60:H60"/>
-    <mergeCell ref="B61:H61"/>
-    <mergeCell ref="B63:H63"/>
+    <mergeCell ref="B62:H62"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B57:I57"/>
-    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B56:I56"/>
+    <mergeCell ref="B57:H57"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
